--- a/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>-6,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>-9,48%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 21,14</t>
+          <t>-1,62; 20,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 8,74</t>
+          <t>-10,02; 8,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 11,49</t>
+          <t>-7,65; 11,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 26,2</t>
+          <t>-29,64; 18,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 70,33</t>
+          <t>-3,33; 69,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 20,47</t>
+          <t>-18,9; 19,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 37,97</t>
+          <t>-19,24; 37,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,25; 187,63</t>
+          <t>-39,72; 35,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,05</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 1,33</t>
+          <t>-12,58; 0,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 3,73</t>
+          <t>-11,07; 3,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 10,19</t>
+          <t>-5,77; 10,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 27,67</t>
+          <t>-13,29; 19,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 2,02</t>
+          <t>-18,11; 1,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 5,9</t>
+          <t>-15,45; 5,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 16,21</t>
+          <t>-7,84; 15,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 130,7</t>
+          <t>-14,72; 26,65</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>-5,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>-6,78%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 4,14</t>
+          <t>-16,59; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 7,09</t>
+          <t>-10,93; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 4,33</t>
+          <t>-11,62; 4,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 31,44</t>
+          <t>-22,76; 10,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 6,13</t>
+          <t>-21,61; 6,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 10,47</t>
+          <t>-14,2; 9,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 6,03</t>
+          <t>-14,75; 6,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 151,45</t>
+          <t>-26,58; 13,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,71%</t>
+          <t>-0,75%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 7,97</t>
+          <t>-6,54; 9,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 14,05</t>
+          <t>-2,59; 13,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 10,93</t>
+          <t>-6,67; 10,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 20,61</t>
+          <t>-19,62; 14,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 11,6</t>
+          <t>-8,53; 13,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 20,87</t>
+          <t>-3,45; 19,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 16,63</t>
+          <t>-8,81; 15,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 81,61</t>
+          <t>-22,37; 18,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 2,73</t>
+          <t>-5,75; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,46</t>
+          <t>-5,22; 3,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,43</t>
+          <t>-3,77; 4,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 16,14</t>
+          <t>-10,84; 6,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 4,34</t>
+          <t>-8,67; 4,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,46</t>
+          <t>-7,63; 5,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 7,0</t>
+          <t>-5,66; 7,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 61,33</t>
+          <t>-13,03; 9,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 20,21</t>
+          <t>-1,43; 20,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 8,24</t>
+          <t>-10,35; 8,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 11,13</t>
+          <t>-8,94; 10,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 18,38</t>
+          <t>-29,28; 16,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 69,57</t>
+          <t>-4,0; 70,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 19,19</t>
+          <t>-19,98; 20,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 37,58</t>
+          <t>-21,11; 32,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 35,14</t>
+          <t>-41,36; 32,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 0,86</t>
+          <t>-13,49; 0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 3,47</t>
+          <t>-10,22; 4,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 10,07</t>
+          <t>-4,61; 9,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 19,35</t>
+          <t>-13,39; 17,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 1,19</t>
+          <t>-19,05; 0,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 5,3</t>
+          <t>-14,26; 6,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 15,87</t>
+          <t>-6,55; 14,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 26,65</t>
+          <t>-15,14; 22,54</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 4,53</t>
+          <t>-16,78; 3,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 6,78</t>
+          <t>-11,23; 6,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 4,21</t>
+          <t>-11,79; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 10,46</t>
+          <t>-23,77; 11,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 6,77</t>
+          <t>-21,87; 5,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 9,72</t>
+          <t>-14,55; 8,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 6,0</t>
+          <t>-14,84; 5,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 13,9</t>
+          <t>-26,84; 15,02</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 9,29</t>
+          <t>-6,33; 9,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 13,09</t>
+          <t>-2,24; 13,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 10,63</t>
+          <t>-7,04; 10,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 14,46</t>
+          <t>-21,57; 15,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 13,48</t>
+          <t>-8,23; 13,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 19,74</t>
+          <t>-3,17; 20,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 15,47</t>
+          <t>-9,05; 15,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 18,87</t>
+          <t>-24,65; 21,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,96</t>
+          <t>-5,9; 3,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,33</t>
+          <t>-4,92; 3,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,62</t>
+          <t>-4,07; 4,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 6,87</t>
+          <t>-11,85; 6,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 4,78</t>
+          <t>-8,89; 4,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,26</t>
+          <t>-7,36; 5,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,4</t>
+          <t>-6,18; 7,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 9,06</t>
+          <t>-14,43; 8,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,02</t>
+          <t>-7,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,48%</t>
+          <t>-11,12%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 20,29</t>
+          <t>-0,63; 21,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 8,8</t>
+          <t>-11,9; 8,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 10,28</t>
+          <t>-8,04; 11,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 16,93</t>
+          <t>-32,56; 15,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 70,14</t>
+          <t>-1,73; 70,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 20,48</t>
+          <t>-23,19; 20,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 32,12</t>
+          <t>-19,08; 37,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 32,4</t>
+          <t>-44,21; 30,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 0,28</t>
+          <t>-13,02; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 4,29</t>
+          <t>-10,17; 3,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 9,55</t>
+          <t>-4,39; 10,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 17,06</t>
+          <t>-13,19; 17,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 0,43</t>
+          <t>-18,66; 2,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 6,93</t>
+          <t>-14,17; 5,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 14,85</t>
+          <t>-6,23; 16,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 22,54</t>
+          <t>-14,99; 23,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,66</t>
+          <t>-7,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-6,78%</t>
+          <t>-9,09%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 3,96</t>
+          <t>-16,01; 4,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 6,3</t>
+          <t>-11,47; 7,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 3,95</t>
+          <t>-11,59; 4,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 11,34</t>
+          <t>-24,81; 10,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 5,93</t>
+          <t>-20,82; 6,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 8,73</t>
+          <t>-14,73; 10,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 5,58</t>
+          <t>-14,74; 6,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 15,02</t>
+          <t>-29,33; 13,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,75%</t>
+          <t>-1,3%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 9,15</t>
+          <t>-6,96; 7,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 13,76</t>
+          <t>-2,84; 14,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 10,23</t>
+          <t>-6,35; 10,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 15,8</t>
+          <t>-22,07; 15,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 13,15</t>
+          <t>-9,18; 11,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 20,5</t>
+          <t>-3,84; 20,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 15,29</t>
+          <t>-8,14; 16,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 21,21</t>
+          <t>-26,11; 20,65</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,01%</t>
+          <t>-4,64%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,05</t>
+          <t>-5,96; 2,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,46</t>
+          <t>-4,94; 3,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,64</t>
+          <t>-3,55; 4,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 6,58</t>
+          <t>-13,51; 5,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 4,85</t>
+          <t>-9,02; 4,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 5,39</t>
+          <t>-7,28; 5,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 7,39</t>
+          <t>-5,35; 7,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 8,67</t>
+          <t>-16,1; 6,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,88</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-11,12%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>9.882221259383977</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.9416556862121117</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.557709780681188</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-7.041408929157356</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2832589131845666</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.01993034360628853</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.04324399735593323</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1112348663037664</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 21,14</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,9; 8,74</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-8,04; 11,49</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-32,56; 15,31</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,73; 70,33</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-23,19; 20,47</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-19,08; 37,97</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-44,21; 30,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.6256618661217098</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.90220035290311</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-8.043353562010234</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-32.55784173659463</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.01734715212290296</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2318869888453066</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1907509125866332</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4421373142372095</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>21.13821212793418</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.736514093859453</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.48602131267005</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>15.30697004121319</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.7032831662535218</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2046649435010291</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.3796992293552974</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.3007604468637937</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-6,41</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,85</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-9,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,56%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-13,02; 1,33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,17; 3,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,39; 10,19</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-13,19; 17,34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-18,66; 2,02</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-14,17; 5,9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 16,21</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-14,99; 23,41</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-6.405333751234843</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.101784172806343</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.854327188443306</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.776078802960301</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.09474980094660695</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04560535063773263</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.04248719023915956</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.02170442500483086</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-6,16</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-8,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-4,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-9,09%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-13.0159594714936</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-10.16612834021728</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.389039306282578</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-13.19468052864609</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1866461752883347</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1416559607713438</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.06229623046337659</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1498750328676068</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-16,01; 4,14</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,47; 7,09</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-11,59; 4,33</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-24,81; 10,3</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-20,82; 6,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-14,73; 10,47</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-14,74; 6,03</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-29,33; 13,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.330769486876189</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.731586557561751</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10.19251422648034</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>17.34011215600804</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.02024196769068515</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.05895728718700333</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1620996062119006</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2340608925454275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,59</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-1,3%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-6.157415587984483</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.154250367223398</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.735511466092256</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-7.545577694075734</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.08580943341464653</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02939206931313002</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.04990322503052163</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.09086144629535158</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,96; 7,97</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 14,05</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,35; 10,93</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-22,07; 15,25</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-9,18; 11,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 20,87</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,14; 16,63</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-26,11; 20,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-16.00825942274513</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.46886508830854</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-11.59417777821332</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-24.81048699961767</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2082208129123195</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1472573248283974</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1474037662059369</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2932558688484667</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.14344751786841</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.086818613777554</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.331071583548189</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.29768580882462</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.06130485481797666</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1047046371896078</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.06034666341926448</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1301964987040918</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.15916552992924</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.587134662983628</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.7550078888803</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.036679003065177</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.01573117705862255</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.07792463499652967</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.02405379046834219</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.0129536464524292</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.957482255704305</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.843952893019992</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.349932677496019</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-22.06723963352156</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.09181957309656873</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.0384358933227054</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.08135694214974579</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2611481513876549</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.966783216468677</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>14.05460236995775</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.92538393160636</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>15.24710267629022</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1159755681336044</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2087033506464776</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1663312878107129</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2064732918023303</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-4,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,96; 2,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 3,46</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 4,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 5,25</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-9,02; 4,34</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,28; 5,46</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 7,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-16,1; 6,92</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.552593652952794</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.6074659246134706</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1766449687071403</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.679345248576305</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.02412439412535567</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.009228237955842399</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.00272224927411034</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.04643755485914103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.961931213498485</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.943711806169215</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.551820528158387</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.51018343728392</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.09015276919207149</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.07277263632068226</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.05353002302638124</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1609911995992762</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.730059343886936</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.458157455785055</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.433756919314734</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.252570675575955</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.04341438361315633</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.0546076436298123</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.06995217201249268</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.06919438222188555</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
